--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487560_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487560_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.935700000000001</v>
+        <v>10.293</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5582</v>
+        <v>11.1293</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.8363</v>
       </c>
       <c r="G2" t="n">
         <v>9.4359</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5037</v>
+        <v>-0.1464</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7546</v>
+        <v>-0.1835</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2509</v>
+        <v>0.0371</v>
       </c>
       <c r="V2" t="n">
         <v>2.7662</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5651</v>
+        <v>3.7536</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0278</v>
+        <v>3.1896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5373</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.8213</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4509</v>
+        <v>-0.2625</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1653</v>
+        <v>0.327</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6162</v>
+        <v>-0.5895</v>
       </c>
       <c r="V3" t="n">
         <v>1.6071</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9336</v>
+        <v>3.2557</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0696</v>
+        <v>3.2313</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.136</v>
+        <v>0.0244</v>
       </c>
       <c r="G4" t="n">
         <v>3.3959</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7953</v>
+        <v>-0.4732</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3564</v>
+        <v>-0.1947</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4389</v>
+        <v>-0.2785</v>
       </c>
       <c r="V4" t="n">
         <v>0.3329</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1343</v>
+        <v>-0.1832</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4982</v>
+        <v>-0.6006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3639</v>
+        <v>0.4174</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4991</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9731</v>
+        <v>0.9243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7287</v>
+        <v>0.6264</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2444</v>
+        <v>0.2979</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7068</v>
+        <v>-0.6666</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0367</v>
+        <v>-0.9608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3299</v>
+        <v>0.2943</v>
       </c>
       <c r="G6" t="n">
         <v>-3.1069</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1247</v>
+        <v>0.165</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3305</v>
+        <v>0.4064</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2058</v>
+        <v>-0.2414</v>
       </c>
       <c r="V6" t="n">
         <v>1.492</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1442</v>
+        <v>-1.2196</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5475</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6917</v>
+        <v>-0.3441</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9213</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7101</v>
+        <v>-0.8639</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6314</v>
+        <v>0.1769</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2172</v>
+        <v>0.0608</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3392</v>
+        <v>0.0204</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.122</v>
+        <v>0.0404</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1385</v>
+        <v>-0.7479</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.629</v>
+        <v>-0.8843</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5095</v>
+        <v>0.1364</v>
       </c>
       <c r="P7" t="n">
         <v>-0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7771</v>
+        <v>-0.1409</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0722</v>
+        <v>0.0429</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2951</v>
+        <v>-0.1838</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4348</v>
+        <v>-1.2463</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0372</v>
+        <v>1.4187</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3976</v>
+        <v>-2.6649</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.9213</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8639</v>
+        <v>0.7101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1769</v>
+        <v>-1.6314</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0608</v>
+        <v>1.2172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0204</v>
+        <v>2.3392</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0404</v>
+        <v>-1.122</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7479</v>
+        <v>-2.1385</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8843</v>
+        <v>-1.629</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1364</v>
+        <v>-0.5095</v>
       </c>
       <c r="P8" t="n">
         <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3561</v>
+        <v>0.675</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>0.9434</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2373</v>
+        <v>-0.2683</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8596</v>
+        <v>-1.7526</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0559</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1963</v>
+        <v>0.3032</v>
       </c>
       <c r="G9" t="n">
         <v>0.2235</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5163</v>
+        <v>-0.4093</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3381</v>
+        <v>-0.2311</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4695</v>
+        <v>-3.1415</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0464</v>
+        <v>-2.8253</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4231</v>
+        <v>-0.3162</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7011</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3767</v>
+        <v>-1.0486</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.517</v>
+        <v>-0.2958</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8597</v>
+        <v>-0.7528</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.478</v>
+        <v>-3.6265</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9706</v>
+        <v>-1.8518</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5074</v>
+        <v>-1.7747</v>
       </c>
       <c r="G11" t="n">
         <v>-2.523</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2488</v>
+        <v>-0.3973</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1911</v>
+        <v>-0.0723</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0576</v>
+        <v>-0.3249</v>
       </c>
       <c r="V11" t="n">
         <v>-2.273</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9679</v>
+        <v>-4.2911</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3177</v>
+        <v>-1.6677</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6502</v>
+        <v>-2.6234</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7247</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3052</v>
+        <v>0.982</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3515</v>
+        <v>1.0016</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0463</v>
+        <v>-0.0196</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1567</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2393000000000001</v>
+        <v>1.174899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>7.240399999999999</v>
+        <v>8.1313</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.001099999999999</v>
+        <v>-6.9563</v>
       </c>
       <c r="G13" t="n">
         <v>3.713500000000002</v>
@@ -1468,13 +1468,13 @@
         <v>15.6678</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.067700000000001</v>
+        <v>-0.1318999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5321</v>
+        <v>2.4232</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5997</v>
+        <v>-2.5549</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4480999999999997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9483</v>
+        <v>7.2626</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4683</v>
+        <v>5.673</v>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>1.5897</v>
       </c>
       <c r="G14" t="n">
         <v>4.0447</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2792</v>
+        <v>0.5936</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1653</v>
+        <v>0.3699</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1139</v>
+        <v>0.2236</v>
       </c>
       <c r="V14" t="n">
         <v>0.6659</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4437</v>
+        <v>4.2061</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4676</v>
+        <v>4.8769</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0239</v>
+        <v>-0.6708</v>
       </c>
       <c r="G15" t="n">
         <v>3.2862</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6882</v>
+        <v>0.0743</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2506</v>
+        <v>0.1588</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4376</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.8249</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.381</v>
+        <v>2.8933</v>
       </c>
       <c r="E16" t="n">
-        <v>3.312</v>
+        <v>2.391</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.5023</v>
       </c>
       <c r="G16" t="n">
         <v>0.6178</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0973</v>
+        <v>0.6096</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4527</v>
+        <v>0.5317</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3553</v>
+        <v>0.0779</v>
       </c>
       <c r="V16" t="n">
         <v>1.2742</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8342000000000001</v>
+        <v>-0.2518</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9559</v>
+        <v>2.3561</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1217</v>
+        <v>-2.6079</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4524</v>
+        <v>0.5151</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6091</v>
+        <v>0.9745</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0615</v>
+        <v>-0.4594</v>
       </c>
       <c r="J17" t="n">
-        <v>1.359</v>
+        <v>2.3859</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4205</v>
+        <v>0.9714</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0615</v>
+        <v>1.4145</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8114</v>
+        <v>-1.8708</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8114</v>
+        <v>0.0031</v>
       </c>
       <c r="O17" t="n">
-        <v>-2</v>
+        <v>-1.8739</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1751</v>
+        <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
         <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3881</v>
+        <v>0.2123</v>
       </c>
       <c r="T17" t="n">
-        <v>1.772</v>
+        <v>0.1994</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.384</v>
+        <v>0.0129</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1152</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0644</v>
+        <v>-0.3376</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4585</v>
+        <v>0.7279</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3941</v>
+        <v>-1.0655</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5151</v>
+        <v>-1.4524</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9745</v>
+        <v>0.6091</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4594</v>
+        <v>-2.0615</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3859</v>
+        <v>1.359</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9714</v>
+        <v>1.4205</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4145</v>
+        <v>-0.0615</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8708</v>
+        <v>-2.8114</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0031</v>
+        <v>-0.8114</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8739</v>
+        <v>-2</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9377</v>
+        <v>-1.1751</v>
       </c>
       <c r="R18" t="n">
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5285</v>
+        <v>0.2163</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3017</v>
+        <v>0.544</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2268</v>
+        <v>-0.3277</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7086</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4512</v>
+        <v>-0.7019</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2469</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2043</v>
+        <v>-0.1481</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3566</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7476</v>
+        <v>0.4968</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7705</v>
+        <v>0.4634</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0229</v>
+        <v>0.0334</v>
       </c>
       <c r="V19" t="n">
         <v>0.9412</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4459</v>
+        <v>-1.8245</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.937</v>
+        <v>-1.4253</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5089</v>
+        <v>-0.3992</v>
       </c>
       <c r="G20" t="n">
         <v>-3.075</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9377</v>
+        <v>-0.3163</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6775</v>
+        <v>-0.1659</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2601</v>
+        <v>-0.1504</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1862</v>
+        <v>-2.6136</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7853</v>
+        <v>-2.3759</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4009</v>
+        <v>-0.2377</v>
       </c>
       <c r="G21" t="n">
         <v>-4.2045</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.825</v>
+        <v>-0.2525</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2153</v>
+        <v>0.1941</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6097</v>
+        <v>-0.4465</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1152</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8139</v>
+        <v>-2.8274</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1149</v>
+        <v>-1.3985</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.699</v>
+        <v>-1.4289</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4512</v>
@@ -2170,13 +2170,13 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0297</v>
+        <v>0.9567</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2023</v>
+        <v>0.514</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1726</v>
+        <v>0.4427</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1578</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0138</v>
+        <v>-4.68</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8525</v>
+        <v>-3.5455</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1613</v>
+        <v>-1.1346</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6374</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4927</v>
+        <v>-0.1589</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.517</v>
+        <v>-0.21</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0243</v>
+        <v>0.051</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1003</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2393999999999998</v>
+        <v>1.125199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>6.725700000000001</v>
+        <v>6.7258</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.965099999999999</v>
+        <v>-5.600700000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-3.713300000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>6.468099999999999</v>
+        <v>6.4681</v>
       </c>
       <c r="I24" t="n">
         <v>-10.1817</v>
@@ -2305,7 +2305,7 @@
         <v>10.1816</v>
       </c>
       <c r="L24" t="n">
-        <v>3.1515</v>
+        <v>3.151500000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-17.0466</v>
@@ -2326,22 +2326,22 @@
         <v>17.6263</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0674</v>
+        <v>2.4319</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5995</v>
+        <v>2.5994</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.532</v>
+        <v>-0.1676</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4481000000000011</v>
+        <v>0.4481000000000002</v>
       </c>
       <c r="W24" t="n">
-        <v>6.461000000000001</v>
+        <v>6.461</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.012899999999999</v>
+        <v>-6.0129</v>
       </c>
     </row>
   </sheetData>
